--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Device.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -490,6 +490,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Device.meta.tag</t>
   </si>
   <si>
@@ -672,6 +679,16 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -725,6 +742,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -757,6 +777,9 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -889,10 +912,16 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1145,6 +1174,9 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1194,6 +1226,16 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1260,6 +1302,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1311,6 +1357,9 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1690,7 +1739,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -3016,13 +3065,13 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
@@ -3033,10 +3082,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3062,13 +3111,13 @@
         <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3094,13 +3143,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3118,7 +3167,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3127,13 +3176,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3144,10 +3193,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3173,13 +3222,13 @@
         <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3229,7 +3278,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3255,10 +3304,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3281,16 +3330,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3316,13 +3365,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3340,7 +3389,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3366,14 +3415,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3392,16 +3441,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3451,7 +3500,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3466,7 +3515,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3477,14 +3526,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3503,16 +3552,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3562,7 +3611,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3577,7 +3626,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3588,10 +3637,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3620,7 +3669,7 @@
         <v>106</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>108</v>
@@ -3661,19 +3710,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3688,7 +3737,7 @@
         <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3699,10 +3748,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3728,16 +3777,16 @@
         <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3774,19 +3823,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3801,7 +3850,7 @@
         <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3812,10 +3861,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3838,16 +3887,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3897,7 +3946,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3906,27 +3955,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3949,15 +3998,17 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -4006,7 +4057,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4015,13 +4066,13 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4032,10 +4083,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4058,16 +4109,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4117,7 +4168,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4126,16 +4177,16 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4143,10 +4194,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4252,10 +4303,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4325,16 +4376,16 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>112</v>
@@ -4363,14 +4414,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4392,16 +4443,16 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4450,7 +4501,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4465,7 +4516,7 @@
         <v>113</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4476,14 +4527,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4505,12 +4556,14 @@
         <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4559,7 +4612,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4574,25 +4627,25 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4614,12 +4667,14 @@
         <v>126</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4668,7 +4723,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4683,21 +4738,21 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4723,14 +4778,16 @@
         <v>126</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4779,7 +4836,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4794,7 +4851,7 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4805,14 +4862,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4831,16 +4888,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4890,7 +4947,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4905,25 +4962,25 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4945,13 +5002,13 @@
         <v>98</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5001,7 +5058,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5016,21 +5073,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5053,17 +5110,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5088,13 +5145,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5112,7 +5169,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5127,7 +5184,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5138,10 +5195,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5164,16 +5221,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5199,13 +5256,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5223,7 +5280,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5238,10 +5295,10 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5249,10 +5306,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5275,15 +5332,17 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5311,10 +5370,10 @@
         <v>148</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5332,7 +5391,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5341,16 +5400,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5358,14 +5417,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5387,13 +5446,13 @@
         <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5443,7 +5502,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5458,21 +5517,21 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5498,12 +5557,14 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5552,7 +5613,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5567,21 +5628,21 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5604,13 +5665,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5661,7 +5722,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5676,21 +5737,21 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5713,13 +5774,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5770,7 +5831,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5785,21 +5846,21 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5825,12 +5886,14 @@
         <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5879,7 +5942,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5894,21 +5957,21 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5934,13 +5997,13 @@
         <v>98</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5990,7 +6053,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6005,10 +6068,10 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6016,10 +6079,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6042,13 +6105,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6099,7 +6162,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6108,13 +6171,13 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
@@ -6125,10 +6188,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6234,10 +6297,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6307,16 +6370,16 @@
         <v>76</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>112</v>
@@ -6345,14 +6408,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6374,16 +6437,16 @@
         <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6432,7 +6495,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6447,7 +6510,7 @@
         <v>113</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6458,14 +6521,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6487,12 +6550,14 @@
         <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6541,7 +6606,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -6567,10 +6632,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6593,13 +6658,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6626,13 +6691,13 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6650,7 +6715,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -6665,10 +6730,10 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6676,10 +6741,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6705,12 +6770,14 @@
         <v>98</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6759,7 +6826,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6774,10 +6841,10 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6785,10 +6852,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6814,13 +6881,13 @@
         <v>98</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6870,7 +6937,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6885,10 +6952,10 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -6896,10 +6963,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6922,15 +6989,17 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6955,13 +7024,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6979,7 +7048,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6988,13 +7057,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -7005,10 +7074,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7031,13 +7100,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7088,7 +7157,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7097,13 +7166,13 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -7114,10 +7183,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7223,10 +7292,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7296,16 +7365,16 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>112</v>
@@ -7334,14 +7403,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7363,16 +7432,16 @@
         <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7421,7 +7490,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7436,7 +7505,7 @@
         <v>113</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7447,14 +7516,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7473,15 +7542,17 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7530,7 +7601,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -7539,13 +7610,13 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7556,10 +7627,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7585,12 +7656,14 @@
         <v>98</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7639,7 +7712,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7657,7 +7730,7 @@
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7665,10 +7738,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7691,13 +7764,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7748,7 +7821,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7757,13 +7830,13 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7774,10 +7847,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7883,10 +7956,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7956,16 +8029,16 @@
         <v>76</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>112</v>
@@ -7994,14 +8067,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8023,16 +8096,16 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8081,7 +8154,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8096,7 +8169,7 @@
         <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8107,14 +8180,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8133,15 +8206,17 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8190,7 +8265,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8199,13 +8274,13 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8216,10 +8291,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8242,13 +8317,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8299,7 +8374,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8308,16 +8383,16 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>76</v>
+        <v>367</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>76</v>
@@ -8325,10 +8400,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8354,12 +8429,14 @@
         <v>98</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8408,7 +8485,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8434,10 +8511,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8460,13 +8537,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8517,7 +8594,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8526,13 +8603,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8543,10 +8620,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8652,10 +8729,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8725,16 +8802,16 @@
         <v>76</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>112</v>
@@ -8763,14 +8840,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8792,16 +8869,16 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8850,7 +8927,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8865,7 +8942,7 @@
         <v>113</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8876,10 +8953,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8902,15 +8979,17 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8959,7 +9038,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -8968,13 +9047,13 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -8985,10 +9064,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9011,15 +9090,17 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9068,7 +9149,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9077,13 +9158,13 @@
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9094,10 +9175,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9120,15 +9201,17 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9177,7 +9260,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9186,13 +9269,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9203,10 +9286,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9229,17 +9312,19 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9288,7 +9373,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9297,16 +9382,16 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>76</v>
@@ -9314,10 +9399,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9340,15 +9425,17 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9397,7 +9484,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9406,16 +9493,16 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -9423,10 +9510,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9449,16 +9536,16 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9508,7 +9595,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9517,16 +9604,16 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>408</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>76</v>
@@ -9534,10 +9621,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9560,17 +9647,19 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9619,7 +9708,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9628,16 +9717,16 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>76</v>
@@ -9645,10 +9734,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9674,13 +9763,13 @@
         <v>126</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9730,7 +9819,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9745,10 +9834,10 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>76</v>
@@ -9756,10 +9845,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9782,15 +9871,17 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -9839,7 +9930,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9848,13 +9939,13 @@
         <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
@@ -9865,10 +9956,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9891,15 +9982,17 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -9948,7 +10041,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -9957,13 +10050,13 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>76</v>
@@ -9974,10 +10067,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10000,15 +10093,17 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10057,7 +10152,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10066,13 +10161,13 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>76</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Device.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2672" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -490,13 +490,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Device.meta.tag</t>
   </si>
   <si>
@@ -679,16 +672,6 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -742,9 +725,6 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -777,9 +757,6 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -912,16 +889,10 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1174,9 +1145,6 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1226,16 +1194,6 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1302,10 +1260,6 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1357,9 +1311,6 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1739,7 +1690,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -3065,13 +3016,13 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
@@ -3082,10 +3033,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3111,13 +3062,13 @@
         <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3143,31 +3094,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3176,13 +3127,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3193,10 +3144,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3222,13 +3173,13 @@
         <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3278,7 +3229,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3304,10 +3255,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3330,16 +3281,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3365,31 +3316,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3415,14 +3366,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3441,16 +3392,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3500,7 +3451,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3515,7 +3466,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3526,14 +3477,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3552,16 +3503,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3611,7 +3562,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3626,7 +3577,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3637,10 +3588,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3669,7 +3620,7 @@
         <v>106</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>108</v>
@@ -3710,19 +3661,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3737,7 +3688,7 @@
         <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3748,10 +3699,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3777,16 +3728,16 @@
         <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3823,19 +3774,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3850,7 +3801,7 @@
         <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3861,10 +3812,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3887,16 +3838,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3946,7 +3897,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3955,27 +3906,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3998,17 +3949,15 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -4057,7 +4006,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4066,13 +4015,13 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4083,10 +4032,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4109,16 +4058,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4168,7 +4117,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4177,16 +4126,16 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4194,10 +4143,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4303,10 +4252,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4376,16 +4325,16 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>112</v>
@@ -4414,14 +4363,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4443,16 +4392,16 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4501,7 +4450,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4516,7 +4465,7 @@
         <v>113</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
@@ -4527,14 +4476,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4556,14 +4505,12 @@
         <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4612,7 +4559,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4627,25 +4574,25 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4667,14 +4614,12 @@
         <v>126</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4723,7 +4668,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4738,21 +4683,21 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4778,16 +4723,14 @@
         <v>126</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4836,7 +4779,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4851,7 +4794,7 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4862,14 +4805,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4888,16 +4831,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4947,7 +4890,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4962,25 +4905,25 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5002,13 +4945,13 @@
         <v>98</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5058,7 +5001,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5073,21 +5016,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5110,17 +5053,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5145,13 +5088,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5169,7 +5112,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5184,7 +5127,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5195,10 +5138,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5221,16 +5164,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5256,13 +5199,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5280,7 +5223,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5295,10 +5238,10 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5306,10 +5249,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5332,17 +5275,15 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5370,10 +5311,10 @@
         <v>148</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5391,7 +5332,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5400,16 +5341,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5417,14 +5358,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5446,13 +5387,13 @@
         <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5502,7 +5443,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5517,21 +5458,21 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5557,14 +5498,12 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5613,7 +5552,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5628,21 +5567,21 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5665,13 +5604,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5722,7 +5661,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5737,21 +5676,21 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5774,13 +5713,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5831,7 +5770,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5846,21 +5785,21 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5886,14 +5825,12 @@
         <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5942,7 +5879,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5957,21 +5894,21 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5997,13 +5934,13 @@
         <v>98</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6053,7 +5990,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6068,10 +6005,10 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6079,10 +6016,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6105,13 +6042,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6162,7 +6099,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6171,13 +6108,13 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
@@ -6188,10 +6125,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6297,10 +6234,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6370,16 +6307,16 @@
         <v>76</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>112</v>
@@ -6408,14 +6345,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6437,16 +6374,16 @@
         <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6495,7 +6432,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6510,7 +6447,7 @@
         <v>113</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6521,14 +6458,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6550,14 +6487,12 @@
         <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6606,7 +6541,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -6632,10 +6567,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6658,13 +6593,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6691,13 +6626,13 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6715,7 +6650,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -6730,10 +6665,10 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6741,10 +6676,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6770,14 +6705,12 @@
         <v>98</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6826,7 +6759,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6841,10 +6774,10 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6852,10 +6785,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6881,13 +6814,13 @@
         <v>98</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6937,7 +6870,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6952,10 +6885,10 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -6963,10 +6896,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6989,17 +6922,15 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7024,13 +6955,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -7048,7 +6979,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7057,13 +6988,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -7074,10 +7005,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7100,13 +7031,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7157,7 +7088,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7166,13 +7097,13 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -7183,10 +7114,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7292,10 +7223,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7365,16 +7296,16 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>112</v>
@@ -7403,14 +7334,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7432,16 +7363,16 @@
         <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7490,7 +7421,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7505,7 +7436,7 @@
         <v>113</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7516,14 +7447,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7542,17 +7473,15 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7601,7 +7530,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -7610,13 +7539,13 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7627,10 +7556,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7656,14 +7585,12 @@
         <v>98</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7712,7 +7639,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7730,7 +7657,7 @@
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -7738,10 +7665,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7764,13 +7691,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7821,7 +7748,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7830,13 +7757,13 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7847,10 +7774,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7956,10 +7883,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8029,16 +7956,16 @@
         <v>76</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>112</v>
@@ -8067,14 +7994,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8096,16 +8023,16 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8154,7 +8081,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8169,7 +8096,7 @@
         <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8180,14 +8107,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8206,17 +8133,15 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8265,7 +8190,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8274,13 +8199,13 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8291,10 +8216,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8317,13 +8242,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8374,7 +8299,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8383,16 +8308,16 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>367</v>
+        <v>76</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>76</v>
@@ -8400,10 +8325,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8429,14 +8354,12 @@
         <v>98</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8485,7 +8408,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -8511,10 +8434,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8537,13 +8460,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8594,7 +8517,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8603,13 +8526,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8620,10 +8543,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8729,10 +8652,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8802,16 +8725,16 @@
         <v>76</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>112</v>
@@ -8840,14 +8763,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8869,16 +8792,16 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>108</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8927,7 +8850,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8942,7 +8865,7 @@
         <v>113</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8953,10 +8876,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8979,17 +8902,15 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9038,7 +8959,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -9047,13 +8968,13 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -9064,10 +8985,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9090,17 +9011,15 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9149,7 +9068,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9158,13 +9077,13 @@
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>385</v>
+        <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>386</v>
+        <v>76</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9175,10 +9094,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9201,17 +9120,15 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9260,7 +9177,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9269,13 +9186,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9286,10 +9203,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9312,19 +9229,17 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9373,7 +9288,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9382,16 +9297,16 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>76</v>
@@ -9399,10 +9314,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9425,17 +9340,15 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9484,7 +9397,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9493,16 +9406,16 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -9510,10 +9423,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9536,16 +9449,16 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9595,7 +9508,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9604,16 +9517,16 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>408</v>
+        <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>76</v>
@@ -9621,10 +9534,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9647,19 +9560,17 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9708,7 +9619,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9717,16 +9628,16 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>76</v>
@@ -9734,10 +9645,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9763,13 +9674,13 @@
         <v>126</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9819,7 +9730,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9834,10 +9745,10 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>76</v>
@@ -9845,10 +9756,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9871,17 +9782,15 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -9930,7 +9839,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9939,13 +9848,13 @@
         <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
@@ -9956,10 +9865,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9982,17 +9891,15 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -10041,7 +9948,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10050,13 +9957,13 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>76</v>
@@ -10067,10 +9974,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10093,17 +10000,15 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10152,7 +10057,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10161,13 +10066,13 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>76</v>
